--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/118.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/118.xlsx
@@ -426,13 +426,13 @@
         <v>-10.08474874079969</v>
       </c>
       <c r="E2">
-        <v>-8.233302182585216</v>
+        <v>-7.152695072504878</v>
       </c>
       <c r="F2">
-        <v>-6.456456880357657</v>
+        <v>-7.018938938858934</v>
       </c>
       <c r="G2">
-        <v>-10.06067952305715</v>
+        <v>-9.584083455587049</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.521222284129141</v>
       </c>
       <c r="E3">
-        <v>-8.619205152096862</v>
+        <v>-8.91515904239415</v>
       </c>
       <c r="F3">
-        <v>-6.562226263626196</v>
+        <v>-6.446597915107568</v>
       </c>
       <c r="G3">
-        <v>-9.892123096925154</v>
+        <v>-9.300872905793478</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.924014864057964</v>
       </c>
       <c r="E4">
-        <v>-9.504956554101152</v>
+        <v>-9.129672856137494</v>
       </c>
       <c r="F4">
-        <v>-6.489739252023575</v>
+        <v>-6.440837976693115</v>
       </c>
       <c r="G4">
-        <v>-10.2154078004716</v>
+        <v>-9.343218093786295</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.356126582042631</v>
       </c>
       <c r="E5">
-        <v>-10.20702852188033</v>
+        <v>-10.61941400738883</v>
       </c>
       <c r="F5">
-        <v>-6.167344238817567</v>
+        <v>-6.471592357791512</v>
       </c>
       <c r="G5">
-        <v>-10.1038622790714</v>
+        <v>-9.953980640326437</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.793432247783741</v>
       </c>
       <c r="E6">
-        <v>-11.33298377067348</v>
+        <v>-10.57467268419304</v>
       </c>
       <c r="F6">
-        <v>-5.787916016331796</v>
+        <v>-6.381608959161595</v>
       </c>
       <c r="G6">
-        <v>-10.25042344064047</v>
+        <v>-9.339113017317599</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.240360014144017</v>
       </c>
       <c r="E7">
-        <v>-11.07029152196253</v>
+        <v>-11.38568162270074</v>
       </c>
       <c r="F7">
-        <v>-6.214590937392872</v>
+        <v>-6.203243288582269</v>
       </c>
       <c r="G7">
-        <v>-10.63650588252136</v>
+        <v>-9.840614318879634</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.700005298349502</v>
       </c>
       <c r="E8">
-        <v>-12.52435282650742</v>
+        <v>-12.14361684583853</v>
       </c>
       <c r="F8">
-        <v>-5.762484866741668</v>
+        <v>-6.477701503360319</v>
       </c>
       <c r="G8">
-        <v>-10.03626756025056</v>
+        <v>-10.03087137102155</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.189597080793876</v>
       </c>
       <c r="E9">
-        <v>-14.38416540213959</v>
+        <v>-12.89259021891515</v>
       </c>
       <c r="F9">
-        <v>-5.876114974321491</v>
+        <v>-6.241231246449436</v>
       </c>
       <c r="G9">
-        <v>-9.948531482368796</v>
+        <v>-9.890911437257781</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.715763063463963</v>
       </c>
       <c r="E10">
-        <v>-14.40705683824836</v>
+        <v>-13.52959254367811</v>
       </c>
       <c r="F10">
-        <v>-5.824010257850576</v>
+        <v>-5.667136268396721</v>
       </c>
       <c r="G10">
-        <v>-10.29113321913689</v>
+        <v>-9.321014264854403</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.293337579688885</v>
       </c>
       <c r="E11">
-        <v>-15.41237806795118</v>
+        <v>-14.01143576351626</v>
       </c>
       <c r="F11">
-        <v>-5.966725124567444</v>
+        <v>-6.474915368728583</v>
       </c>
       <c r="G11">
-        <v>-9.357076037413684</v>
+        <v>-7.767938036016111</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.929390835238986</v>
       </c>
       <c r="E12">
-        <v>-14.99477125191184</v>
+        <v>-14.74060159128332</v>
       </c>
       <c r="F12">
-        <v>-5.845066419849301</v>
+        <v>-5.904567042945319</v>
       </c>
       <c r="G12">
-        <v>-9.315515448713674</v>
+        <v>-8.362932454152704</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.623332570118154</v>
       </c>
       <c r="E13">
-        <v>-15.65501823375617</v>
+        <v>-15.92642779493188</v>
       </c>
       <c r="F13">
-        <v>-5.716824249640676</v>
+        <v>-5.7583901950973</v>
       </c>
       <c r="G13">
-        <v>-8.470425867812839</v>
+        <v>-8.245795421336672</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.379216949428874</v>
       </c>
       <c r="E14">
-        <v>-17.71391158371353</v>
+        <v>-16.35870233828207</v>
       </c>
       <c r="F14">
-        <v>-5.548326650620454</v>
+        <v>-6.03472391360571</v>
       </c>
       <c r="G14">
-        <v>-8.125712002990687</v>
+        <v>-8.099267365222989</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.200493329230834</v>
       </c>
       <c r="E15">
-        <v>-17.92085831739006</v>
+        <v>-17.07251211068913</v>
       </c>
       <c r="F15">
-        <v>-5.35608375695709</v>
+        <v>-5.806216530037656</v>
       </c>
       <c r="G15">
-        <v>-7.748534928610443</v>
+        <v>-6.763359613215348</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.087439343191912</v>
       </c>
       <c r="E16">
-        <v>-18.2519124097208</v>
+        <v>-19.02081559690517</v>
       </c>
       <c r="F16">
-        <v>-5.204466087436579</v>
+        <v>-5.280252750314019</v>
       </c>
       <c r="G16">
-        <v>-6.664589487051192</v>
+        <v>-5.823105090242624</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.045111776353123</v>
       </c>
       <c r="E17">
-        <v>-19.20347612447857</v>
+        <v>-18.81325751923761</v>
       </c>
       <c r="F17">
-        <v>-5.068113759234989</v>
+        <v>-5.381899747084669</v>
       </c>
       <c r="G17">
-        <v>-5.913671684560466</v>
+        <v>-5.485873058339226</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.077596518411023</v>
       </c>
       <c r="E18">
-        <v>-19.81371516785619</v>
+        <v>-20.2526737388417</v>
       </c>
       <c r="F18">
-        <v>-4.769072073458051</v>
+        <v>-5.020158352262525</v>
       </c>
       <c r="G18">
-        <v>-5.339831652419816</v>
+        <v>-5.130293983057186</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.182898088183268</v>
       </c>
       <c r="E19">
-        <v>-21.63177974161164</v>
+        <v>-21.3930612342973</v>
       </c>
       <c r="F19">
-        <v>-4.554956617396553</v>
+        <v>-4.703694317709838</v>
       </c>
       <c r="G19">
-        <v>-4.8341590634783</v>
+        <v>-4.699436412757659</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.355955945072417</v>
       </c>
       <c r="E20">
-        <v>-22.58626885057836</v>
+        <v>-20.36584483276739</v>
       </c>
       <c r="F20">
-        <v>-4.160788052102829</v>
+        <v>-4.3327832656373</v>
       </c>
       <c r="G20">
-        <v>-4.655796801458986</v>
+        <v>-5.693556822199864</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.588255904534546</v>
       </c>
       <c r="E21">
-        <v>-22.9566980244058</v>
+        <v>-21.3252835638245</v>
       </c>
       <c r="F21">
-        <v>-4.181780074011979</v>
+        <v>-4.00016859815896</v>
       </c>
       <c r="G21">
-        <v>-5.022684700303175</v>
+        <v>-5.007558817734246</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.867294748656272</v>
       </c>
       <c r="E22">
-        <v>-23.90117467734156</v>
+        <v>-22.65748816129699</v>
       </c>
       <c r="F22">
-        <v>-3.94345054635637</v>
+        <v>-3.603049588744772</v>
       </c>
       <c r="G22">
-        <v>-4.737391817365403</v>
+        <v>-5.148339766791753</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.179818968926961</v>
       </c>
       <c r="E23">
-        <v>-23.80870776657894</v>
+        <v>-24.28273484027985</v>
       </c>
       <c r="F23">
-        <v>-3.436525287295188</v>
+        <v>-3.722848230865232</v>
       </c>
       <c r="G23">
-        <v>-5.315763986349315</v>
+        <v>-4.787162559002805</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.514364216727489</v>
       </c>
       <c r="E24">
-        <v>-23.09557273679902</v>
+        <v>-24.72677435910196</v>
       </c>
       <c r="F24">
-        <v>-3.188725198265251</v>
+        <v>-3.312818850828382</v>
       </c>
       <c r="G24">
-        <v>-4.907669727177816</v>
+        <v>-4.772854381182076</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.859918011556808</v>
       </c>
       <c r="E25">
-        <v>-23.92346382640731</v>
+        <v>-23.95011389594245</v>
       </c>
       <c r="F25">
-        <v>-2.968581365636632</v>
+        <v>-3.089856813523239</v>
       </c>
       <c r="G25">
-        <v>-4.92146145989442</v>
+        <v>-5.439174502962266</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.204734446728456</v>
       </c>
       <c r="E26">
-        <v>-25.53695911534026</v>
+        <v>-23.70846093747114</v>
       </c>
       <c r="F26">
-        <v>-2.846016781134858</v>
+        <v>-2.837165448773467</v>
       </c>
       <c r="G26">
-        <v>-6.009899311750462</v>
+        <v>-5.659319160232721</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.539865445887469</v>
       </c>
       <c r="E27">
-        <v>-25.25541935780938</v>
+        <v>-23.92444650526697</v>
       </c>
       <c r="F27">
-        <v>-2.835000522787062</v>
+        <v>-2.886303884064765</v>
       </c>
       <c r="G27">
-        <v>-4.736663497346763</v>
+        <v>-5.813646861636927</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.858499925757027</v>
       </c>
       <c r="E28">
-        <v>-25.2401991566696</v>
+        <v>-24.86292745861658</v>
       </c>
       <c r="F28">
-        <v>-2.946028601547817</v>
+        <v>-2.824669217247692</v>
       </c>
       <c r="G28">
-        <v>-5.311010042954921</v>
+        <v>-6.375870189480273</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.153498873200457</v>
       </c>
       <c r="E29">
-        <v>-25.2169952558543</v>
+        <v>-24.6544184014074</v>
       </c>
       <c r="F29">
-        <v>-2.874361157756436</v>
+        <v>-2.889343015716493</v>
       </c>
       <c r="G29">
-        <v>-5.98392477144934</v>
+        <v>-6.062139720360161</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.421504289967494</v>
       </c>
       <c r="E30">
-        <v>-24.49982082725955</v>
+        <v>-23.51701517032286</v>
       </c>
       <c r="F30">
-        <v>-3.001621430297488</v>
+        <v>-3.056249782144656</v>
       </c>
       <c r="G30">
-        <v>-5.754156358296223</v>
+        <v>-5.620363970872117</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.661025483125632</v>
       </c>
       <c r="E31">
-        <v>-24.50787698251919</v>
+        <v>-23.66630990140774</v>
       </c>
       <c r="F31">
-        <v>-3.24497130570504</v>
+        <v>-2.763316450083568</v>
       </c>
       <c r="G31">
-        <v>-5.789801002117556</v>
+        <v>-6.412378885687356</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.866865997730711</v>
       </c>
       <c r="E32">
-        <v>-24.39165369711233</v>
+        <v>-24.25079098462974</v>
       </c>
       <c r="F32">
-        <v>-3.12089111464219</v>
+        <v>-3.073134462762114</v>
       </c>
       <c r="G32">
-        <v>-5.612968212137385</v>
+        <v>-6.48722038869366</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.0343848778578</v>
       </c>
       <c r="E33">
-        <v>-24.10837500556251</v>
+        <v>-24.24421111189659</v>
       </c>
       <c r="F33">
-        <v>-2.795563869933746</v>
+        <v>-3.13399707294541</v>
       </c>
       <c r="G33">
-        <v>-5.098784210614403</v>
+        <v>-5.670790200526296</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.160818693521517</v>
       </c>
       <c r="E34">
-        <v>-23.95178943132529</v>
+        <v>-23.96432424737852</v>
       </c>
       <c r="F34">
-        <v>-2.932826829036714</v>
+        <v>-2.683575273535276</v>
       </c>
       <c r="G34">
-        <v>-5.535557725792607</v>
+        <v>-5.6697705525002</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.241445103607754</v>
       </c>
       <c r="E35">
-        <v>-23.31226021806605</v>
+        <v>-22.10644533014763</v>
       </c>
       <c r="F35">
-        <v>-3.2379151039988</v>
+        <v>-2.890195841351957</v>
       </c>
       <c r="G35">
-        <v>-4.711566251613548</v>
+        <v>-5.111529810940596</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.27461418334639</v>
       </c>
       <c r="E36">
-        <v>-23.08945476841466</v>
+        <v>-22.3968382543635</v>
       </c>
       <c r="F36">
-        <v>-2.934952954228191</v>
+        <v>-3.282906605350519</v>
       </c>
       <c r="G36">
-        <v>-5.16824938766493</v>
+        <v>-5.350918669430835</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.262483173562138</v>
       </c>
       <c r="E37">
-        <v>-22.18234255451619</v>
+        <v>-22.25166443462561</v>
       </c>
       <c r="F37">
-        <v>-3.253330897379688</v>
+        <v>-3.393590228074667</v>
       </c>
       <c r="G37">
-        <v>-4.459123912061963</v>
+        <v>-5.237287504340891</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.205525008811653</v>
       </c>
       <c r="E38">
-        <v>-20.98089311554116</v>
+        <v>-22.01906842416964</v>
       </c>
       <c r="F38">
-        <v>-3.204802980718792</v>
+        <v>-3.518501072890164</v>
       </c>
       <c r="G38">
-        <v>-4.706669954760966</v>
+        <v>-5.333482026075494</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.107730352403731</v>
       </c>
       <c r="E39">
-        <v>-21.14018218876097</v>
+        <v>-20.38364626409155</v>
       </c>
       <c r="F39">
-        <v>-3.168927290616342</v>
+        <v>-3.346384705853163</v>
       </c>
       <c r="G39">
-        <v>-4.859454941943871</v>
+        <v>-4.76697485230433</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.976056283015118</v>
       </c>
       <c r="E40">
-        <v>-21.72954496696324</v>
+        <v>-20.61837065733112</v>
       </c>
       <c r="F40">
-        <v>-3.135547521036625</v>
+        <v>-3.406006482451712</v>
       </c>
       <c r="G40">
-        <v>-4.362482466679558</v>
+        <v>-4.95248458214293</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.814436666092146</v>
       </c>
       <c r="E41">
-        <v>-20.12323183780645</v>
+        <v>-19.75478613559438</v>
       </c>
       <c r="F41">
-        <v>-3.33484978381806</v>
+        <v>-3.340676237880961</v>
       </c>
       <c r="G41">
-        <v>-3.993237459411407</v>
+        <v>-4.389827572833939</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.628549080109917</v>
       </c>
       <c r="E42">
-        <v>-19.69874174127545</v>
+        <v>-19.99409787300372</v>
       </c>
       <c r="F42">
-        <v>-3.489134414100171</v>
+        <v>-2.923585905020125</v>
       </c>
       <c r="G42">
-        <v>-3.942509970113155</v>
+        <v>-4.350749893288381</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.424656434925655</v>
       </c>
       <c r="E43">
-        <v>-19.18357800968886</v>
+        <v>-18.55023922039811</v>
       </c>
       <c r="F43">
-        <v>-3.44578600763572</v>
+        <v>-3.349883112220369</v>
       </c>
       <c r="G43">
-        <v>-3.506852108781684</v>
+        <v>-3.806946440825539</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.203721628295958</v>
       </c>
       <c r="E44">
-        <v>-18.01913073183051</v>
+        <v>-18.88454475706636</v>
       </c>
       <c r="F44">
-        <v>-3.436327324055758</v>
+        <v>-3.700053159771354</v>
       </c>
       <c r="G44">
-        <v>-3.243862371141982</v>
+        <v>-3.947830016794764</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.969228922549457</v>
       </c>
       <c r="E45">
-        <v>-18.75232690146441</v>
+        <v>-18.23495327456208</v>
       </c>
       <c r="F45">
-        <v>-3.480325049945539</v>
+        <v>-3.569787013402798</v>
       </c>
       <c r="G45">
-        <v>-3.233364631236952</v>
+        <v>-4.61948673798426</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.726164139794601</v>
       </c>
       <c r="E46">
-        <v>-17.84055488781204</v>
+        <v>-16.75054666569178</v>
       </c>
       <c r="F46">
-        <v>-3.26099761771633</v>
+        <v>-3.510603923342825</v>
       </c>
       <c r="G46">
-        <v>-3.513992955509893</v>
+        <v>-3.929787543605736</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.475922089092726</v>
       </c>
       <c r="E47">
-        <v>-17.92244781176675</v>
+        <v>-16.63671441456097</v>
       </c>
       <c r="F47">
-        <v>-3.357986143536715</v>
+        <v>-3.55491284744499</v>
       </c>
       <c r="G47">
-        <v>-3.425660979431059</v>
+        <v>-4.179809874368114</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.2241027332378</v>
       </c>
       <c r="E48">
-        <v>-16.46134473013993</v>
+        <v>-16.35816797834917</v>
       </c>
       <c r="F48">
-        <v>-3.684932727543696</v>
+        <v>-3.37718778590846</v>
       </c>
       <c r="G48">
-        <v>-3.48207267542024</v>
+        <v>-3.855628012980522</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.976909570224429</v>
       </c>
       <c r="E49">
-        <v>-16.12476137104582</v>
+        <v>-15.56386458045577</v>
       </c>
       <c r="F49">
-        <v>-4.009544137178362</v>
+        <v>-3.844279673784509</v>
       </c>
       <c r="G49">
-        <v>-3.358427110074</v>
+        <v>-4.574251443735657</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.736097846271865</v>
       </c>
       <c r="E50">
-        <v>-16.45504562279526</v>
+        <v>-14.78272998497668</v>
       </c>
       <c r="F50">
-        <v>-3.755012506154849</v>
+        <v>-3.972882928941854</v>
       </c>
       <c r="G50">
-        <v>-3.525593107079499</v>
+        <v>-4.1366304288994</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.507123121481048</v>
       </c>
       <c r="E51">
-        <v>-15.3454381651698</v>
+        <v>-16.19759734698519</v>
       </c>
       <c r="F51">
-        <v>-3.91851351301186</v>
+        <v>-4.131462569666636</v>
       </c>
       <c r="G51">
-        <v>-3.381445333208553</v>
+        <v>-3.747591669851946</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.296187585960316</v>
       </c>
       <c r="E52">
-        <v>-13.83459432504272</v>
+        <v>-15.36901340085373</v>
       </c>
       <c r="F52">
-        <v>-3.983393193249668</v>
+        <v>-4.101527360453001</v>
       </c>
       <c r="G52">
-        <v>-3.748902645885497</v>
+        <v>-3.168765956129154</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.105324524072006</v>
       </c>
       <c r="E53">
-        <v>-14.17742697826741</v>
+        <v>-14.1101746107795</v>
       </c>
       <c r="F53">
-        <v>-3.853945030986436</v>
+        <v>-4.009932936980602</v>
       </c>
       <c r="G53">
-        <v>-2.854989139371491</v>
+        <v>-3.702253748691627</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.940531940382046</v>
       </c>
       <c r="E54">
-        <v>-13.61286665220516</v>
+        <v>-12.99429068817941</v>
       </c>
       <c r="F54">
-        <v>-4.143465476799753</v>
+        <v>-3.904018644620801</v>
       </c>
       <c r="G54">
-        <v>-3.103154254086338</v>
+        <v>-4.235370760153702</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.808839927017117</v>
       </c>
       <c r="E55">
-        <v>-12.8889040410729</v>
+        <v>-12.87232076925681</v>
       </c>
       <c r="F55">
-        <v>-4.118005820503148</v>
+        <v>-4.327815972033523</v>
       </c>
       <c r="G55">
-        <v>-3.691256116410168</v>
+        <v>-3.941414179539656</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.712440713476048</v>
       </c>
       <c r="E56">
-        <v>-11.73443751992746</v>
+        <v>-13.27410509711336</v>
       </c>
       <c r="F56">
-        <v>-3.651280560546523</v>
+        <v>-4.202937593189292</v>
       </c>
       <c r="G56">
-        <v>-4.022684761983225</v>
+        <v>-3.681632360527507</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.655980907317798</v>
       </c>
       <c r="E57">
-        <v>-12.53434716864235</v>
+        <v>-12.59956172282681</v>
       </c>
       <c r="F57">
-        <v>-4.163124018328102</v>
+        <v>-4.624585039821806</v>
       </c>
       <c r="G57">
-        <v>-3.799971121374295</v>
+        <v>-3.783756069322945</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.643702081736215</v>
       </c>
       <c r="E58">
-        <v>-12.315105628035</v>
+        <v>-11.2563665189377</v>
       </c>
       <c r="F58">
-        <v>-4.498088113531995</v>
+        <v>-4.4852307970575</v>
       </c>
       <c r="G58">
-        <v>-4.025300092959249</v>
+        <v>-4.400245859646025</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.673368618645342</v>
       </c>
       <c r="E59">
-        <v>-11.46652394068567</v>
+        <v>-10.4870331267226</v>
       </c>
       <c r="F59">
-        <v>-4.236178788501409</v>
+        <v>-4.300790822439507</v>
       </c>
       <c r="G59">
-        <v>-3.81802683674548</v>
+        <v>-3.306239670192929</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.742969964415615</v>
       </c>
       <c r="E60">
-        <v>-11.19460266194709</v>
+        <v>-10.22520128807311</v>
       </c>
       <c r="F60">
-        <v>-4.289635197971152</v>
+        <v>-4.797985792356229</v>
       </c>
       <c r="G60">
-        <v>-4.253191426791599</v>
+        <v>-4.555993785086577</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.848198629784958</v>
       </c>
       <c r="E61">
-        <v>-11.1183341027099</v>
+        <v>-11.39208941342159</v>
       </c>
       <c r="F61">
-        <v>-4.573979300999854</v>
+        <v>-4.847760877425533</v>
       </c>
       <c r="G61">
-        <v>-3.852155250709826</v>
+        <v>-4.296152376254721</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.977288378397224</v>
       </c>
       <c r="E62">
-        <v>-10.66842568157384</v>
+        <v>-10.09204150987756</v>
       </c>
       <c r="F62">
-        <v>-4.929715282990651</v>
+        <v>-4.65643099022242</v>
       </c>
       <c r="G62">
-        <v>-4.569504121432343</v>
+        <v>-3.701548602491763</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.117852872920973</v>
       </c>
       <c r="E63">
-        <v>-10.07196678460156</v>
+        <v>-11.32111011182537</v>
       </c>
       <c r="F63">
-        <v>-4.765678191681264</v>
+        <v>-4.717746540297532</v>
       </c>
       <c r="G63">
-        <v>-4.581365806099551</v>
+        <v>-4.830630021933437</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.256346756389068</v>
       </c>
       <c r="E64">
-        <v>-8.60993536580316</v>
+        <v>-10.42199971149845</v>
       </c>
       <c r="F64">
-        <v>-4.83811135728276</v>
+        <v>-4.619616954365073</v>
       </c>
       <c r="G64">
-        <v>-4.528152097101306</v>
+        <v>-4.274200148783814</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.376351390534754</v>
       </c>
       <c r="E65">
-        <v>-9.303475688551883</v>
+        <v>-9.655329061999854</v>
       </c>
       <c r="F65">
-        <v>-4.667284126860927</v>
+        <v>-4.545329269136596</v>
       </c>
       <c r="G65">
-        <v>-5.122835323957208</v>
+        <v>-4.77197046552309</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.465463232199506</v>
       </c>
       <c r="E66">
-        <v>-9.070449473065182</v>
+        <v>-9.891507095395895</v>
       </c>
       <c r="F66">
-        <v>-5.072817365803845</v>
+        <v>-4.676607403585119</v>
       </c>
       <c r="G66">
-        <v>-4.563323332910524</v>
+        <v>-5.169411389149214</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.514126786091378</v>
       </c>
       <c r="E67">
-        <v>-9.364270452104858</v>
+        <v>-10.06241623291938</v>
       </c>
       <c r="F67">
-        <v>-5.111468500523102</v>
+        <v>-5.119343478187624</v>
       </c>
       <c r="G67">
-        <v>-4.556963774929583</v>
+        <v>-4.891812214044707</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.514076175609996</v>
       </c>
       <c r="E68">
-        <v>-8.224947148041066</v>
+        <v>-10.46703085703072</v>
       </c>
       <c r="F68">
-        <v>-5.111144632663394</v>
+        <v>-5.167070831508266</v>
       </c>
       <c r="G68">
-        <v>-5.316336710727609</v>
+        <v>-3.958801164711908</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.464515310295456</v>
       </c>
       <c r="E69">
-        <v>-8.790399583482833</v>
+        <v>-9.906496344361283</v>
       </c>
       <c r="F69">
-        <v>-4.621323397488958</v>
+        <v>-5.375816732663465</v>
       </c>
       <c r="G69">
-        <v>-4.631444428472107</v>
+        <v>-4.945244419048544</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.370675637332079</v>
       </c>
       <c r="E70">
-        <v>-8.437445790850997</v>
+        <v>-8.960602279061122</v>
       </c>
       <c r="F70">
-        <v>-4.816601463539262</v>
+        <v>-4.945651323764761</v>
       </c>
       <c r="G70">
-        <v>-5.117293470724467</v>
+        <v>-4.088832772403402</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.239140724806653</v>
       </c>
       <c r="E71">
-        <v>-9.029697735470156</v>
+        <v>-8.5272454304231</v>
       </c>
       <c r="F71">
-        <v>-4.939361635721593</v>
+        <v>-5.253390722429293</v>
       </c>
       <c r="G71">
-        <v>-4.840826502194392</v>
+        <v>-4.514155110561268</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.080005379476799</v>
       </c>
       <c r="E72">
-        <v>-8.987533113984737</v>
+        <v>-9.913977383421955</v>
       </c>
       <c r="F72">
-        <v>-4.914338290404692</v>
+        <v>-5.353746207025901</v>
       </c>
       <c r="G72">
-        <v>-4.487806478614209</v>
+        <v>-4.448583135064924</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.903211048025897</v>
       </c>
       <c r="E73">
-        <v>-8.640099531168254</v>
+        <v>-9.48138131841722</v>
       </c>
       <c r="F73">
-        <v>-5.539168871164425</v>
+        <v>-5.416067410357317</v>
       </c>
       <c r="G73">
-        <v>-4.085015713396622</v>
+        <v>-3.409988856848149</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.712454939454028</v>
       </c>
       <c r="E74">
-        <v>-9.547886487693868</v>
+        <v>-9.362603973670035</v>
       </c>
       <c r="F74">
-        <v>-5.130274216415987</v>
+        <v>-5.067393964896422</v>
       </c>
       <c r="G74">
-        <v>-4.405135535407529</v>
+        <v>-4.17514862624882</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.507905640641264</v>
       </c>
       <c r="E75">
-        <v>-9.417946454517775</v>
+        <v>-9.925928026328197</v>
       </c>
       <c r="F75">
-        <v>-5.282781136808017</v>
+        <v>-5.719908516910994</v>
       </c>
       <c r="G75">
-        <v>-3.815778976324315</v>
+        <v>-4.070389723204122</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.285500795452047</v>
       </c>
       <c r="E76">
-        <v>-9.777620502576992</v>
+        <v>-10.20492730994077</v>
       </c>
       <c r="F76">
-        <v>-5.528186662493811</v>
+        <v>-5.778999752027871</v>
       </c>
       <c r="G76">
-        <v>-4.425700644297481</v>
+        <v>-3.654257459463274</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.035289546393956</v>
       </c>
       <c r="E77">
-        <v>-10.35107022311631</v>
+        <v>-10.81921028060724</v>
       </c>
       <c r="F77">
-        <v>-5.8111600680527</v>
+        <v>-5.619254503749325</v>
       </c>
       <c r="G77">
-        <v>-3.787338079596436</v>
+        <v>-4.519316251056992</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.749132569551162</v>
       </c>
       <c r="E78">
-        <v>-10.1721773859173</v>
+        <v>-12.20397687588677</v>
       </c>
       <c r="F78">
-        <v>-5.520860438928987</v>
+        <v>-5.979165926386178</v>
       </c>
       <c r="G78">
-        <v>-4.37824066344649</v>
+        <v>-4.474849003373501</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.422581289826464</v>
       </c>
       <c r="E79">
-        <v>-10.88588753189618</v>
+        <v>-11.63682173421812</v>
       </c>
       <c r="F79">
-        <v>-5.903956524314917</v>
+        <v>-5.542867616329934</v>
       </c>
       <c r="G79">
-        <v>-4.010766798041848</v>
+        <v>-3.435311219678034</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.053162648717583</v>
       </c>
       <c r="E80">
-        <v>-12.43753745130638</v>
+        <v>-11.61730401124506</v>
       </c>
       <c r="F80">
-        <v>-6.113830815934867</v>
+        <v>-5.470595988731812</v>
       </c>
       <c r="G80">
-        <v>-3.471167738413881</v>
+        <v>-3.680169099399149</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.646090075565976</v>
       </c>
       <c r="E81">
-        <v>-11.93351829425267</v>
+        <v>-12.22956728250412</v>
       </c>
       <c r="F81">
-        <v>-5.853467187877749</v>
+        <v>-6.264379879888936</v>
       </c>
       <c r="G81">
-        <v>-2.914198246341356</v>
+        <v>-4.220628900867327</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.214169801489962</v>
       </c>
       <c r="E82">
-        <v>-13.26716747493361</v>
+        <v>-14.01210144919538</v>
       </c>
       <c r="F82">
-        <v>-6.116846587924344</v>
+        <v>-5.851492306601196</v>
       </c>
       <c r="G82">
-        <v>-3.621579064445128</v>
+        <v>-2.844345735462734</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.773044248780269</v>
       </c>
       <c r="E83">
-        <v>-14.26157508227794</v>
+        <v>-14.89478254582247</v>
       </c>
       <c r="F83">
-        <v>-6.096498342469819</v>
+        <v>-6.064640118348361</v>
       </c>
       <c r="G83">
-        <v>-3.425005491414283</v>
+        <v>-3.625412676179604</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.342185324030501</v>
       </c>
       <c r="E84">
-        <v>-14.32340686637867</v>
+        <v>-15.79077735603212</v>
       </c>
       <c r="F84">
-        <v>-6.232792469479017</v>
+        <v>-6.124496679348874</v>
       </c>
       <c r="G84">
-        <v>-3.067122276436911</v>
+        <v>-3.507838651352387</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.9426853897600168</v>
       </c>
       <c r="E85">
-        <v>-16.08415001614503</v>
+        <v>-17.06776174145508</v>
       </c>
       <c r="F85">
-        <v>-6.395701962176611</v>
+        <v>-6.321702907351225</v>
       </c>
       <c r="G85">
-        <v>-2.97055697360191</v>
+        <v>-2.614223093936916</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5935593050819509</v>
       </c>
       <c r="E86">
-        <v>-18.28305019699754</v>
+        <v>-16.87608955060642</v>
       </c>
       <c r="F86">
-        <v>-6.429389762556881</v>
+        <v>-6.31690546620688</v>
       </c>
       <c r="G86">
-        <v>-3.535832624432464</v>
+        <v>-3.587629419939902</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.3120887250655646</v>
       </c>
       <c r="E87">
-        <v>-19.5654008241196</v>
+        <v>-19.65447590785047</v>
       </c>
       <c r="F87">
-        <v>-6.737015134395501</v>
+        <v>-6.321640746894043</v>
       </c>
       <c r="G87">
-        <v>-3.054029068829093</v>
+        <v>-2.95933422422378</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.1131121238122815</v>
       </c>
       <c r="E88">
-        <v>-20.59575998661083</v>
+        <v>-21.14572051247235</v>
       </c>
       <c r="F88">
-        <v>-6.557587588999874</v>
+        <v>-6.364543340143298</v>
       </c>
       <c r="G88">
-        <v>-3.353726135408235</v>
+        <v>-3.412445281638288</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.009456816751087964</v>
       </c>
       <c r="E89">
-        <v>-22.38404984376584</v>
+        <v>-22.44011688045481</v>
       </c>
       <c r="F89">
-        <v>-6.616125714825784</v>
+        <v>-6.547431282964161</v>
       </c>
       <c r="G89">
-        <v>-3.005013131574644</v>
+        <v>-3.541698911128053</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.009813750117141973</v>
       </c>
       <c r="E90">
-        <v>-23.51186629537614</v>
+        <v>-22.74111096232263</v>
       </c>
       <c r="F90">
-        <v>-6.876807667771905</v>
+        <v>-6.659072255914191</v>
       </c>
       <c r="G90">
-        <v>-3.356166007470678</v>
+        <v>-2.731777255490897</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1202333240703425</v>
       </c>
       <c r="E91">
-        <v>-25.7570791799051</v>
+        <v>-25.20100068565921</v>
       </c>
       <c r="F91">
-        <v>-6.355469497100787</v>
+        <v>-6.498349861085819</v>
       </c>
       <c r="G91">
-        <v>-3.557288270072481</v>
+        <v>-2.684347069549758</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3497572392933671</v>
       </c>
       <c r="E92">
-        <v>-27.37838608650128</v>
+        <v>-26.74566316967557</v>
       </c>
       <c r="F92">
-        <v>-6.408889877260955</v>
+        <v>-6.675507955904622</v>
       </c>
       <c r="G92">
-        <v>-3.546284016699944</v>
+        <v>-4.394104797670677</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.7031057877523571</v>
       </c>
       <c r="E93">
-        <v>-29.65394427535563</v>
+        <v>-29.10526077916427</v>
       </c>
       <c r="F93">
-        <v>-6.391728048108295</v>
+        <v>-6.257006541073129</v>
       </c>
       <c r="G93">
-        <v>-4.186351512353713</v>
+        <v>-3.476325568364065</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.181435643929431</v>
       </c>
       <c r="E94">
-        <v>-32.20585032629107</v>
+        <v>-31.60586601230381</v>
       </c>
       <c r="F94">
-        <v>-6.404752445556869</v>
+        <v>-6.502168967900902</v>
       </c>
       <c r="G94">
-        <v>-4.097923530454241</v>
+        <v>-4.360360406988885</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.785284046492746</v>
       </c>
       <c r="E95">
-        <v>-34.17523385901282</v>
+        <v>-34.18583048819077</v>
       </c>
       <c r="F95">
-        <v>-6.288991857594302</v>
+        <v>-6.223830277703545</v>
       </c>
       <c r="G95">
-        <v>-4.757546418608485</v>
+        <v>-3.974635504026243</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.514561801027166</v>
       </c>
       <c r="E96">
-        <v>-36.80579723922449</v>
+        <v>-35.26144269144065</v>
       </c>
       <c r="F96">
-        <v>-5.860886850091584</v>
+        <v>-6.462622247486463</v>
       </c>
       <c r="G96">
-        <v>-4.948554964587816</v>
+        <v>-4.475223095019439</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.343272930520368</v>
       </c>
       <c r="E97">
-        <v>-38.71214667799647</v>
+        <v>-39.33287593141287</v>
       </c>
       <c r="F97">
-        <v>-5.96119799092256</v>
+        <v>-6.095350155681126</v>
       </c>
       <c r="G97">
-        <v>-5.969331886712232</v>
+        <v>-5.235499809749685</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.272139746467285</v>
       </c>
       <c r="E98">
-        <v>-41.79908740446415</v>
+        <v>-40.82380580709121</v>
       </c>
       <c r="F98">
-        <v>-5.776302700853877</v>
+        <v>-5.762271066443084</v>
       </c>
       <c r="G98">
-        <v>-5.854260634312705</v>
+        <v>-6.258468313021099</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.239904974700893</v>
       </c>
       <c r="E99">
-        <v>-43.9147066840786</v>
+        <v>-44.14841669914046</v>
       </c>
       <c r="F99">
-        <v>-5.43732232744843</v>
+        <v>-5.755987713223578</v>
       </c>
       <c r="G99">
-        <v>-6.789747971708879</v>
+        <v>-6.82367444239533</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.250090463900404</v>
       </c>
       <c r="E100">
-        <v>-45.96610314531627</v>
+        <v>-45.85122255245268</v>
       </c>
       <c r="F100">
-        <v>-5.014951919065518</v>
+        <v>-5.663550758204166</v>
       </c>
       <c r="G100">
-        <v>-7.298294114178483</v>
+        <v>-7.234764745279869</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.189133246422217</v>
       </c>
       <c r="E101">
-        <v>-49.47808983849939</v>
+        <v>-48.87286608008527</v>
       </c>
       <c r="F101">
-        <v>-4.923189622766083</v>
+        <v>-5.275053443793631</v>
       </c>
       <c r="G101">
-        <v>-7.635387103169232</v>
+        <v>-7.497969668379624</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.137852538076082</v>
       </c>
       <c r="E102">
-        <v>-51.37755599677972</v>
+        <v>-51.5673500030337</v>
       </c>
       <c r="F102">
-        <v>-4.812380887274616</v>
+        <v>-5.381248843953423</v>
       </c>
       <c r="G102">
-        <v>-7.686352951746312</v>
+        <v>-7.774790865282402</v>
       </c>
     </row>
   </sheetData>
